--- a/statistics_files/2026/2026_99_gb_requests.xlsx
+++ b/statistics_files/2026/2026_99_gb_requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247FBF24-A06D-40C7-B2E7-31EBDDC36723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63349A3F-9052-4DE7-A912-5150B1106BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5988,39 +5988,39 @@
       </c>
       <c r="B2" s="4">
         <f>SUM(January:December!B2)</f>
-        <v>19500</v>
+        <v>22580</v>
       </c>
       <c r="C2" s="4">
         <f>SUM(January:December!C2)</f>
-        <v>8659</v>
+        <v>10012</v>
       </c>
       <c r="D2" s="4">
         <f>SUM(January:December!D2)</f>
-        <v>647</v>
+        <v>755</v>
       </c>
       <c r="E2" s="4">
         <f>SUM(January:December!E2)</f>
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F2" s="4">
         <f>SUM(January:December!F2)</f>
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="G2" s="4">
         <f>SUM(January:December!G2)</f>
-        <v>1059</v>
+        <v>1218</v>
       </c>
       <c r="H2" s="4">
         <f>SUM(January:December!H2)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I2" s="4">
         <f>SUM(January:December!I2)</f>
-        <v>2874</v>
+        <v>3346</v>
       </c>
       <c r="J2" s="5">
         <f>SUM(January:December!J2)</f>
-        <v>16626</v>
+        <v>19234</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6029,15 +6029,15 @@
       </c>
       <c r="B3" s="7">
         <f>SUM(January:December!B3)</f>
-        <v>8328</v>
+        <v>9548</v>
       </c>
       <c r="C3" s="7">
         <f>SUM(January:December!C3)</f>
-        <v>3651</v>
+        <v>4171</v>
       </c>
       <c r="D3" s="7">
         <f>SUM(January:December!D3)</f>
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(January:December!E3)</f>
@@ -6045,23 +6045,23 @@
       </c>
       <c r="F3" s="7">
         <f>SUM(January:December!F3)</f>
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="G3" s="7">
         <f>SUM(January:December!G3)</f>
-        <v>532</v>
+        <v>593</v>
       </c>
       <c r="H3" s="7">
         <f>SUM(January:December!H3)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I3" s="7">
         <f>SUM(January:December!I3)</f>
-        <v>1308</v>
+        <v>1512</v>
       </c>
       <c r="J3" s="8">
         <f>SUM(January:December!J3)</f>
-        <v>7020</v>
+        <v>8036</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6070,27 +6070,27 @@
       </c>
       <c r="B4" s="10">
         <f>SUM(January:December!B4)</f>
-        <v>17842</v>
+        <v>21028</v>
       </c>
       <c r="C4" s="10">
         <f>SUM(January:December!C4)</f>
-        <v>7878</v>
+        <v>9130</v>
       </c>
       <c r="D4" s="10">
         <f>SUM(January:December!D4)</f>
-        <v>937</v>
+        <v>1053</v>
       </c>
       <c r="E4" s="10">
         <f>SUM(January:December!E4)</f>
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F4" s="10">
         <f>SUM(January:December!F4)</f>
-        <v>634</v>
+        <v>710</v>
       </c>
       <c r="G4" s="10">
         <f>SUM(January:December!G4)</f>
-        <v>1658</v>
+        <v>1875</v>
       </c>
       <c r="H4" s="10">
         <f>SUM(January:December!H4)</f>
@@ -6098,11 +6098,11 @@
       </c>
       <c r="I4" s="10">
         <f>SUM(January:December!I4)</f>
-        <v>2958</v>
+        <v>3450</v>
       </c>
       <c r="J4" s="11">
         <f>SUM(January:December!J4)</f>
-        <v>14884</v>
+        <v>17578</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6111,15 +6111,15 @@
       </c>
       <c r="B5" s="7">
         <f>SUM(January:December!B5)</f>
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(January:December!C5)</f>
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D5" s="7">
         <f>SUM(January:December!D5)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E5" s="7">
         <f>SUM(January:December!E5)</f>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G5" s="7">
         <f>SUM(January:December!G5)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H5" s="7">
         <f>SUM(January:December!H5)</f>
@@ -6139,11 +6139,11 @@
       </c>
       <c r="I5" s="7">
         <f>SUM(January:December!I5)</f>
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="J5" s="8">
         <f>SUM(January:December!J5)</f>
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6152,39 +6152,39 @@
       </c>
       <c r="B6" s="10">
         <f>SUM(January:December!B6)</f>
-        <v>18424</v>
+        <v>21506</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(January:December!C6)</f>
-        <v>7541</v>
+        <v>8635</v>
       </c>
       <c r="D6" s="10">
         <f>SUM(January:December!D6)</f>
-        <v>1929</v>
+        <v>2154</v>
       </c>
       <c r="E6" s="10">
         <f>SUM(January:December!E6)</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F6" s="10">
         <f>SUM(January:December!F6)</f>
-        <v>470</v>
+        <v>543</v>
       </c>
       <c r="G6" s="10">
         <f>SUM(January:December!G6)</f>
-        <v>2434</v>
+        <v>2741</v>
       </c>
       <c r="H6" s="10">
         <f>SUM(January:December!H6)</f>
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="I6" s="10">
         <f>SUM(January:December!I6)</f>
-        <v>5630</v>
+        <v>6474</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(January:December!J6)</f>
-        <v>12794</v>
+        <v>15032</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6193,39 +6193,39 @@
       </c>
       <c r="B7" s="7">
         <f>SUM(January:December!B7)</f>
-        <v>2536</v>
+        <v>2998</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(January:December!C7)</f>
-        <v>1183</v>
+        <v>1372</v>
       </c>
       <c r="D7" s="7">
         <f>SUM(January:December!D7)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" s="7">
         <f>SUM(January:December!E7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7">
         <f>SUM(January:December!F7)</f>
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="G7" s="7">
         <f>SUM(January:December!G7)</f>
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="H7" s="7">
         <f>SUM(January:December!H7)</f>
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="I7" s="7">
         <f>SUM(January:December!I7)</f>
-        <v>852</v>
+        <v>1026</v>
       </c>
       <c r="J7" s="8">
         <f>SUM(January:December!J7)</f>
-        <v>1684</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6234,27 +6234,27 @@
       </c>
       <c r="B8" s="10">
         <f>SUM(January:December!B8)</f>
-        <v>1642</v>
+        <v>1844</v>
       </c>
       <c r="C8" s="10">
         <f>SUM(January:December!C8)</f>
-        <v>717</v>
+        <v>825</v>
       </c>
       <c r="D8" s="10">
         <f>SUM(January:December!D8)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="10">
         <f>SUM(January:December!E8)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="10">
         <f>SUM(January:December!F8)</f>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G8" s="10">
         <f>SUM(January:December!G8)</f>
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H8" s="10">
         <f>SUM(January:December!H8)</f>
@@ -6262,11 +6262,11 @@
       </c>
       <c r="I8" s="10">
         <f>SUM(January:December!I8)</f>
-        <v>434</v>
+        <v>488</v>
       </c>
       <c r="J8" s="11">
         <f>SUM(January:December!J8)</f>
-        <v>1208</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6275,15 +6275,15 @@
       </c>
       <c r="B9" s="7">
         <f>SUM(January:December!B9)</f>
-        <v>652</v>
+        <v>806</v>
       </c>
       <c r="C9" s="7">
         <f>SUM(January:December!C9)</f>
-        <v>323</v>
+        <v>396</v>
       </c>
       <c r="D9" s="7">
         <f>SUM(January:December!D9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="7">
         <f>SUM(January:December!E9)</f>
@@ -6291,11 +6291,11 @@
       </c>
       <c r="F9" s="7">
         <f>SUM(January:December!F9)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="7">
         <f>SUM(January:December!G9)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" s="7">
         <f>SUM(January:December!H9)</f>
@@ -6303,11 +6303,11 @@
       </c>
       <c r="I9" s="7">
         <f>SUM(January:December!I9)</f>
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="J9" s="8">
         <f>SUM(January:December!J9)</f>
-        <v>482</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6398,15 +6398,15 @@
       </c>
       <c r="B12" s="13">
         <f>SUM(January:December!B12)</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C12" s="13">
         <f>SUM(January:December!C12)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="13">
         <f>SUM(January:December!D12)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="13">
         <f>SUM(January:December!E12)</f>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="G12" s="13">
         <f>SUM(January:December!G12)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="13">
         <f>SUM(January:December!H12)</f>
@@ -6426,11 +6426,11 @@
       </c>
       <c r="I12" s="13">
         <f>SUM(January:December!I12)</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J12" s="14">
         <f>SUM(January:December!J12)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6439,27 +6439,27 @@
       </c>
       <c r="B13" s="16">
         <f>SUM(January:December!B13)</f>
-        <v>778</v>
+        <v>890</v>
       </c>
       <c r="C13" s="16">
         <f>SUM(January:December!C13)</f>
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="D13" s="16">
         <f>SUM(January:December!D13)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" s="16">
         <f>SUM(January:December!E13)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="16">
         <f>SUM(January:December!F13)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(January:December!G13)</f>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H13" s="16">
         <f>SUM(January:December!H13)</f>
@@ -6467,11 +6467,11 @@
       </c>
       <c r="I13" s="16">
         <f>SUM(January:December!I13)</f>
-        <v>362</v>
+        <v>418</v>
       </c>
       <c r="J13" s="17">
         <f>SUM(January:December!J13)</f>
-        <v>416</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,15 +6480,15 @@
       </c>
       <c r="B14" s="13">
         <f>SUM(January:December!B14)</f>
-        <v>2596</v>
+        <v>2888</v>
       </c>
       <c r="C14" s="13">
         <f>SUM(January:December!C14)</f>
-        <v>1222</v>
+        <v>1371</v>
       </c>
       <c r="D14" s="13">
         <f>SUM(January:December!D14)</f>
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E14" s="13">
         <f>SUM(January:December!E14)</f>
@@ -6496,11 +6496,11 @@
       </c>
       <c r="F14" s="13">
         <f>SUM(January:December!F14)</f>
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G14" s="13">
         <f>SUM(January:December!G14)</f>
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H14" s="13">
         <f>SUM(January:December!H14)</f>
@@ -6508,11 +6508,11 @@
       </c>
       <c r="I14" s="13">
         <f>SUM(January:December!I14)</f>
-        <v>1248</v>
+        <v>1410</v>
       </c>
       <c r="J14" s="14">
         <f>SUM(January:December!J14)</f>
-        <v>1348</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6521,15 +6521,15 @@
       </c>
       <c r="B15" s="16">
         <f>SUM(January:December!B15)</f>
-        <v>844</v>
+        <v>1012</v>
       </c>
       <c r="C15" s="16">
         <f>SUM(January:December!C15)</f>
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="D15" s="16">
         <f>SUM(January:December!D15)</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E15" s="16">
         <f>SUM(January:December!E15)</f>
@@ -6537,11 +6537,11 @@
       </c>
       <c r="F15" s="16">
         <f>SUM(January:December!F15)</f>
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G15" s="16">
         <f>SUM(January:December!G15)</f>
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H15" s="16">
         <f>SUM(January:December!H15)</f>
@@ -6549,11 +6549,11 @@
       </c>
       <c r="I15" s="16">
         <f>SUM(January:December!I15)</f>
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="J15" s="17">
         <f>SUM(January:December!J15)</f>
-        <v>462</v>
+        <v>574</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6562,19 +6562,19 @@
       </c>
       <c r="B16" s="10">
         <f>SUM(January:December!B16)</f>
-        <v>834</v>
+        <v>1022</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(January:December!C16)</f>
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="D16" s="10">
         <f>SUM(January:December!D16)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="10">
         <f>SUM(January:December!E16)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="10">
         <f>SUM(January:December!F16)</f>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="G16" s="10">
         <f>SUM(January:December!G16)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H16" s="10">
         <f>SUM(January:December!H16)</f>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="I16" s="10">
         <f>SUM(January:December!I16)</f>
-        <v>424</v>
+        <v>490</v>
       </c>
       <c r="J16" s="11">
         <f>SUM(January:December!J16)</f>
-        <v>410</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6603,39 +6603,39 @@
       </c>
       <c r="B17" s="7">
         <f>SUM(January:December!B17)</f>
-        <v>8622</v>
+        <v>9958</v>
       </c>
       <c r="C17" s="7">
         <f>SUM(January:December!C17)</f>
-        <v>3577</v>
+        <v>4209</v>
       </c>
       <c r="D17" s="7">
         <f>SUM(January:December!D17)</f>
-        <v>418</v>
+        <v>485</v>
       </c>
       <c r="E17" s="7">
         <f>SUM(January:December!E17)</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F17" s="7">
         <f>SUM(January:December!F17)</f>
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G17" s="7">
         <f>SUM(January:December!G17)</f>
-        <v>659</v>
+        <v>764</v>
       </c>
       <c r="H17" s="7">
         <f>SUM(January:December!H17)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="7">
         <f>SUM(January:December!I17)</f>
-        <v>2582</v>
+        <v>2936</v>
       </c>
       <c r="J17" s="8">
         <f>SUM(January:December!J17)</f>
-        <v>6040</v>
+        <v>7022</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6644,11 +6644,11 @@
       </c>
       <c r="B18" s="10">
         <f>SUM(January:December!B18)</f>
-        <v>554</v>
+        <v>636</v>
       </c>
       <c r="C18" s="10">
         <f>SUM(January:December!C18)</f>
-        <v>304</v>
+        <v>346</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(January:December!D18)</f>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="F18" s="10">
         <f>SUM(January:December!F18)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(January:December!G18)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(January:December!H18)</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="I18" s="10">
         <f>SUM(January:December!I18)</f>
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="J18" s="11">
         <f>SUM(January:December!J18)</f>
-        <v>420</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6685,27 +6685,27 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(January:December!B19)</f>
-        <v>6182</v>
+        <v>7100</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(January:December!C19)</f>
-        <v>2707</v>
+        <v>3039</v>
       </c>
       <c r="D19" s="7">
         <f>SUM(January:December!D19)</f>
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="E19" s="7">
         <f>SUM(January:December!E19)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="7">
         <f>SUM(January:December!F19)</f>
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G19" s="7">
         <f>SUM(January:December!G19)</f>
-        <v>362</v>
+        <v>418</v>
       </c>
       <c r="H19" s="7">
         <f>SUM(January:December!H19)</f>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="I19" s="7">
         <f>SUM(January:December!I19)</f>
-        <v>1816</v>
+        <v>2058</v>
       </c>
       <c r="J19" s="8">
         <f>SUM(January:December!J19)</f>
-        <v>4366</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6726,11 +6726,11 @@
       </c>
       <c r="B20" s="10">
         <f>SUM(January:December!B20)</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C20" s="10">
         <f>SUM(January:December!C20)</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D20" s="10">
         <f>SUM(January:December!D20)</f>
@@ -6742,11 +6742,11 @@
       </c>
       <c r="F20" s="10">
         <f>SUM(January:December!F20)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="10">
         <f>SUM(January:December!G20)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="10">
         <f>SUM(January:December!H20)</f>
@@ -6754,11 +6754,11 @@
       </c>
       <c r="I20" s="10">
         <f>SUM(January:December!I20)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(January:December!J20)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6767,39 +6767,39 @@
       </c>
       <c r="B21" s="7">
         <f>SUM(January:December!B21)</f>
-        <v>6552</v>
+        <v>7141</v>
       </c>
       <c r="C21" s="7">
         <f>SUM(January:December!C21)</f>
-        <v>2994</v>
+        <v>3457</v>
       </c>
       <c r="D21" s="7">
         <f>SUM(January:December!D21)</f>
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(January:December!E21)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="7">
         <f>SUM(January:December!F21)</f>
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="G21" s="7">
         <f>SUM(January:December!G21)</f>
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="H21" s="7">
         <f>SUM(January:December!H21)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
         <f>SUM(January:December!I21)</f>
-        <v>1604</v>
+        <v>1754</v>
       </c>
       <c r="J21" s="8">
         <f>SUM(January:December!J21)</f>
-        <v>4948</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B22" s="10">
         <f>SUM(January:December!B22)</f>
-        <v>928</v>
+        <v>1050</v>
       </c>
       <c r="C22" s="10">
         <f>SUM(January:December!C22)</f>
-        <v>449</v>
+        <v>507</v>
       </c>
       <c r="D22" s="10">
         <f>SUM(January:December!D22)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(January:December!E22)</f>
@@ -6824,11 +6824,11 @@
       </c>
       <c r="F22" s="10">
         <f>SUM(January:December!F22)</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G22" s="10">
         <f>SUM(January:December!G22)</f>
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H22" s="10">
         <f>SUM(January:December!H22)</f>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="I22" s="10">
         <f>SUM(January:December!I22)</f>
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="J22" s="11">
         <f>SUM(January:December!J22)</f>
-        <v>618</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6849,39 +6849,39 @@
       </c>
       <c r="B23" s="7">
         <f>SUM(January:December!B23)</f>
-        <v>8910</v>
+        <v>10586</v>
       </c>
       <c r="C23" s="7">
         <f>SUM(January:December!C23)</f>
-        <v>2931</v>
+        <v>3498</v>
       </c>
       <c r="D23" s="7">
         <f>SUM(January:December!D23)</f>
-        <v>1086</v>
+        <v>1259</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(January:December!E23)</f>
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F23" s="7">
         <f>SUM(January:December!F23)</f>
-        <v>267</v>
+        <v>310</v>
       </c>
       <c r="G23" s="7">
         <f>SUM(January:December!G23)</f>
-        <v>1445</v>
+        <v>1674</v>
       </c>
       <c r="H23" s="7">
         <f>SUM(January:December!H23)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I23" s="7">
         <f>SUM(January:December!I23)</f>
-        <v>1940</v>
+        <v>2246</v>
       </c>
       <c r="J23" s="8">
         <f>SUM(January:December!J23)</f>
-        <v>6970</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6890,39 +6890,39 @@
       </c>
       <c r="B24" s="10">
         <f>SUM(January:December!B24)</f>
-        <v>27364</v>
+        <v>32254</v>
       </c>
       <c r="C24" s="10">
         <f>SUM(January:December!C24)</f>
-        <v>11627</v>
+        <v>13404</v>
       </c>
       <c r="D24" s="10">
         <f>SUM(January:December!D24)</f>
-        <v>1303</v>
+        <v>1546</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(January:December!E24)</f>
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="F24" s="10">
         <f>SUM(January:December!F24)</f>
-        <v>675</v>
+        <v>769</v>
       </c>
       <c r="G24" s="10">
         <f>SUM(January:December!G24)</f>
-        <v>2103</v>
+        <v>2526</v>
       </c>
       <c r="H24" s="10">
         <f>SUM(January:December!H24)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I24" s="10">
         <f>SUM(January:December!I24)</f>
-        <v>3734</v>
+        <v>4254</v>
       </c>
       <c r="J24" s="11">
         <f>SUM(January:December!J24)</f>
-        <v>23630</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6931,39 +6931,39 @@
       </c>
       <c r="B25" s="7">
         <f>SUM(January:December!B25)</f>
-        <v>1900</v>
+        <v>2196</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(January:December!C25)</f>
-        <v>800</v>
+        <v>939</v>
       </c>
       <c r="D25" s="7">
         <f>SUM(January:December!D25)</f>
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(January:December!E25)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F25" s="7">
         <f>SUM(January:December!F25)</f>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G25" s="7">
         <f>SUM(January:December!G25)</f>
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="H25" s="7">
         <f>SUM(January:December!H25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="7">
         <f>SUM(January:December!I25)</f>
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="J25" s="8">
         <f>SUM(January:December!J25)</f>
-        <v>1308</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -7013,15 +7013,15 @@
       </c>
       <c r="B27" s="7">
         <f>SUM(January:December!B27)</f>
-        <v>2322</v>
+        <v>2582</v>
       </c>
       <c r="C27" s="7">
         <f>SUM(January:December!C27)</f>
-        <v>1107</v>
+        <v>1249</v>
       </c>
       <c r="D27" s="7">
         <f>SUM(January:December!D27)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(January:December!E27)</f>
@@ -7029,23 +7029,23 @@
       </c>
       <c r="F27" s="7">
         <f>SUM(January:December!F27)</f>
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G27" s="7">
         <f>SUM(January:December!G27)</f>
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H27" s="7">
         <f>SUM(January:December!H27)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
         <f>SUM(January:December!I27)</f>
-        <v>702</v>
+        <v>826</v>
       </c>
       <c r="J27" s="8">
         <f>SUM(January:December!J27)</f>
-        <v>1620</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -7054,27 +7054,27 @@
       </c>
       <c r="B28" s="10">
         <f>SUM(January:December!B28)</f>
-        <v>1803</v>
+        <v>2173</v>
       </c>
       <c r="C28" s="10">
         <f>SUM(January:December!C28)</f>
-        <v>794</v>
+        <v>931</v>
       </c>
       <c r="D28" s="10">
         <f>SUM(January:December!D28)</f>
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(January:December!E28)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="10">
         <f>SUM(January:December!F28)</f>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G28" s="10">
         <f>SUM(January:December!G28)</f>
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="H28" s="10">
         <f>SUM(January:December!H28)</f>
@@ -7082,11 +7082,11 @@
       </c>
       <c r="I28" s="10">
         <f>SUM(January:December!I28)</f>
-        <v>580</v>
+        <v>686</v>
       </c>
       <c r="J28" s="11">
         <f>SUM(January:December!J28)</f>
-        <v>1223</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -7095,15 +7095,15 @@
       </c>
       <c r="B29" s="7">
         <f>SUM(January:December!B29)</f>
-        <v>9392</v>
+        <v>10548</v>
       </c>
       <c r="C29" s="7">
         <f>SUM(January:December!C29)</f>
-        <v>4368</v>
+        <v>4889</v>
       </c>
       <c r="D29" s="7">
         <f>SUM(January:December!D29)</f>
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(January:December!E29)</f>
@@ -7111,11 +7111,11 @@
       </c>
       <c r="F29" s="7">
         <f>SUM(January:December!F29)</f>
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="G29" s="7">
         <f>SUM(January:December!G29)</f>
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="H29" s="7">
         <f>SUM(January:December!H29)</f>
@@ -7123,11 +7123,11 @@
       </c>
       <c r="I29" s="7">
         <f>SUM(January:December!I29)</f>
-        <v>2324</v>
+        <v>2506</v>
       </c>
       <c r="J29" s="8">
         <f>SUM(January:December!J29)</f>
-        <v>7068</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -7136,11 +7136,11 @@
       </c>
       <c r="B30" s="10">
         <f>SUM(January:December!B30)</f>
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="C30" s="10">
         <f>SUM(January:December!C30)</f>
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D30" s="10">
         <f>SUM(January:December!D30)</f>
@@ -7152,11 +7152,11 @@
       </c>
       <c r="F30" s="10">
         <f>SUM(January:December!F30)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G30" s="10">
         <f>SUM(January:December!G30)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H30" s="10">
         <f>SUM(January:December!H30)</f>
@@ -7164,11 +7164,11 @@
       </c>
       <c r="I30" s="10">
         <f>SUM(January:December!I30)</f>
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="J30" s="11">
         <f>SUM(January:December!J30)</f>
-        <v>214</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,15 +7177,15 @@
       </c>
       <c r="B31" s="7">
         <f>SUM(January:December!B31)</f>
-        <v>1076</v>
+        <v>1120</v>
       </c>
       <c r="C31" s="7">
         <f>SUM(January:December!C31)</f>
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="D31" s="7">
         <f>SUM(January:December!D31)</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" s="7">
         <f>SUM(January:December!E31)</f>
@@ -7193,23 +7193,23 @@
       </c>
       <c r="F31" s="7">
         <f>SUM(January:December!F31)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G31" s="7">
         <f>SUM(January:December!G31)</f>
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H31" s="7">
         <f>SUM(January:December!H31)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="7">
         <f>SUM(January:December!I31)</f>
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J31" s="8">
         <f>SUM(January:December!J31)</f>
-        <v>958</v>
+        <v>986</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -7218,39 +7218,39 @@
       </c>
       <c r="B32" s="10">
         <f>SUM(January:December!B32)</f>
-        <v>6936</v>
+        <v>8284</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(January:December!C32)</f>
-        <v>2514</v>
+        <v>2966</v>
       </c>
       <c r="D32" s="10">
         <f>SUM(January:December!D32)</f>
-        <v>571</v>
+        <v>650</v>
       </c>
       <c r="E32" s="10">
         <f>SUM(January:December!E32)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F32" s="10">
         <f>SUM(January:December!F32)</f>
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="G32" s="10">
         <f>SUM(January:December!G32)</f>
-        <v>921</v>
+        <v>1060</v>
       </c>
       <c r="H32" s="10">
         <f>SUM(January:December!H32)</f>
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I32" s="10">
         <f>SUM(January:December!I32)</f>
-        <v>2810</v>
+        <v>3244</v>
       </c>
       <c r="J32" s="11">
         <f>SUM(January:December!J32)</f>
-        <v>4126</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -7259,15 +7259,15 @@
       </c>
       <c r="B33" s="7">
         <f>SUM(January:December!B33)</f>
-        <v>5678</v>
+        <v>6862</v>
       </c>
       <c r="C33" s="7">
         <f>SUM(January:December!C33)</f>
-        <v>2427</v>
+        <v>2817</v>
       </c>
       <c r="D33" s="7">
         <f>SUM(January:December!D33)</f>
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E33" s="7">
         <f>SUM(January:December!E33)</f>
@@ -7275,23 +7275,23 @@
       </c>
       <c r="F33" s="7">
         <f>SUM(January:December!F33)</f>
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="G33" s="7">
         <f>SUM(January:December!G33)</f>
-        <v>422</v>
+        <v>488</v>
       </c>
       <c r="H33" s="7">
         <f>SUM(January:December!H33)</f>
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="I33" s="7">
         <f>SUM(January:December!I33)</f>
-        <v>2396</v>
+        <v>2894</v>
       </c>
       <c r="J33" s="8">
         <f>SUM(January:December!J33)</f>
-        <v>3282</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -7300,27 +7300,27 @@
       </c>
       <c r="B34" s="10">
         <f>SUM(January:December!B34)</f>
-        <v>1768</v>
+        <v>2014</v>
       </c>
       <c r="C34" s="10">
         <f>SUM(January:December!C34)</f>
-        <v>791</v>
+        <v>925</v>
       </c>
       <c r="D34" s="10">
         <f>SUM(January:December!D34)</f>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E34" s="10">
         <f>SUM(January:December!E34)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="10">
         <f>SUM(January:December!F34)</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G34" s="10">
         <f>SUM(January:December!G34)</f>
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="H34" s="10">
         <f>SUM(January:December!H34)</f>
@@ -7328,11 +7328,11 @@
       </c>
       <c r="I34" s="10">
         <f>SUM(January:December!I34)</f>
-        <v>692</v>
+        <v>754</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(January:December!J34)</f>
-        <v>1076</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -7341,39 +7341,39 @@
       </c>
       <c r="B35" s="7">
         <f>SUM(January:December!B35)</f>
-        <v>19238</v>
+        <v>22376</v>
       </c>
       <c r="C35" s="7">
         <f>SUM(January:December!C35)</f>
-        <v>7793</v>
+        <v>9057</v>
       </c>
       <c r="D35" s="7">
         <f>SUM(January:December!D35)</f>
-        <v>1361</v>
+        <v>1531</v>
       </c>
       <c r="E35" s="7">
         <f>SUM(January:December!E35)</f>
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F35" s="7">
         <f>SUM(January:December!F35)</f>
-        <v>470</v>
+        <v>537</v>
       </c>
       <c r="G35" s="7">
         <f>SUM(January:December!G35)</f>
-        <v>1896</v>
+        <v>2149</v>
       </c>
       <c r="H35" s="7">
         <f>SUM(January:December!H35)</f>
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="I35" s="7">
         <f>SUM(January:December!I35)</f>
-        <v>4114</v>
+        <v>4630</v>
       </c>
       <c r="J35" s="8">
         <f>SUM(January:December!J35)</f>
-        <v>15124</v>
+        <v>17746</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -7382,15 +7382,15 @@
       </c>
       <c r="B36" s="10">
         <f>SUM(January:December!B36)</f>
-        <v>2256</v>
+        <v>2644</v>
       </c>
       <c r="C36" s="10">
         <f>SUM(January:December!C36)</f>
-        <v>1029</v>
+        <v>1190</v>
       </c>
       <c r="D36" s="10">
         <f>SUM(January:December!D36)</f>
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E36" s="10">
         <f>SUM(January:December!E36)</f>
@@ -7398,11 +7398,11 @@
       </c>
       <c r="F36" s="10">
         <f>SUM(January:December!F36)</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G36" s="10">
         <f>SUM(January:December!G36)</f>
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="H36" s="10">
         <f>SUM(January:December!H36)</f>
@@ -7410,11 +7410,11 @@
       </c>
       <c r="I36" s="10">
         <f>SUM(January:December!I36)</f>
-        <v>794</v>
+        <v>884</v>
       </c>
       <c r="J36" s="11">
         <f>SUM(January:December!J36)</f>
-        <v>1462</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7423,39 +7423,39 @@
       </c>
       <c r="B37" s="7">
         <f>SUM(January:December!B37)</f>
-        <v>7996</v>
+        <v>9254</v>
       </c>
       <c r="C37" s="7">
         <f>SUM(January:December!C37)</f>
-        <v>2941</v>
+        <v>3415</v>
       </c>
       <c r="D37" s="7">
         <f>SUM(January:December!D37)</f>
-        <v>759</v>
+        <v>861</v>
       </c>
       <c r="E37" s="7">
         <f>SUM(January:December!E37)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F37" s="7">
         <f>SUM(January:December!F37)</f>
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G37" s="7">
         <f>SUM(January:December!G37)</f>
-        <v>1041</v>
+        <v>1167</v>
       </c>
       <c r="H37" s="7">
         <f>SUM(January:December!H37)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I37" s="7">
         <f>SUM(January:December!I37)</f>
-        <v>2020</v>
+        <v>2254</v>
       </c>
       <c r="J37" s="8">
         <f>SUM(January:December!J37)</f>
-        <v>5976</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -7464,11 +7464,11 @@
       </c>
       <c r="B38" s="10">
         <f>SUM(January:December!B38)</f>
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="C38" s="10">
         <f>SUM(January:December!C38)</f>
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="D38" s="10">
         <f>SUM(January:December!D38)</f>
@@ -7480,11 +7480,11 @@
       </c>
       <c r="F38" s="10">
         <f>SUM(January:December!F38)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G38" s="10">
         <f>SUM(January:December!G38)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H38" s="10">
         <f>SUM(January:December!H38)</f>
@@ -7492,11 +7492,11 @@
       </c>
       <c r="I38" s="10">
         <f>SUM(January:December!I38)</f>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J38" s="11">
         <f>SUM(January:December!J38)</f>
-        <v>327</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -7505,15 +7505,15 @@
       </c>
       <c r="B39" s="7">
         <f>SUM(January:December!B39)</f>
-        <v>2175</v>
+        <v>2381</v>
       </c>
       <c r="C39" s="7">
         <f>SUM(January:December!C39)</f>
-        <v>451</v>
+        <v>504</v>
       </c>
       <c r="D39" s="7">
         <f>SUM(January:December!D39)</f>
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="E39" s="7">
         <f>SUM(January:December!E39)</f>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="G39" s="7">
         <f>SUM(January:December!G39)</f>
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="H39" s="7">
         <f>SUM(January:December!H39)</f>
@@ -7533,11 +7533,11 @@
       </c>
       <c r="I39" s="7">
         <f>SUM(January:December!I39)</f>
-        <v>1060</v>
+        <v>1136</v>
       </c>
       <c r="J39" s="8">
         <f>SUM(January:December!J39)</f>
-        <v>1115</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -7546,11 +7546,11 @@
       </c>
       <c r="B40" s="19">
         <f>SUM(January:December!B40)</f>
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C40" s="19">
         <f>SUM(January:December!C40)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D40" s="19">
         <f>SUM(January:December!D40)</f>
@@ -7574,11 +7574,11 @@
       </c>
       <c r="I40" s="19">
         <f>SUM(January:December!I40)</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J40" s="20">
         <f>SUM(January:December!J40)</f>
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -7587,15 +7587,15 @@
       </c>
       <c r="B41" s="22">
         <f>SUM(January:December!B41)</f>
-        <v>880</v>
+        <v>930</v>
       </c>
       <c r="C41" s="22">
         <f>SUM(January:December!C41)</f>
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D41" s="22">
         <f>SUM(January:December!D41)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" s="22">
         <f>SUM(January:December!E41)</f>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="G41" s="22">
         <f>SUM(January:December!G41)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H41" s="22">
         <f>SUM(January:December!H41)</f>
@@ -7615,11 +7615,11 @@
       </c>
       <c r="I41" s="22">
         <f>SUM(January:December!I41)</f>
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="J41" s="23">
         <f>SUM(January:December!J41)</f>
-        <v>432</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="B42" s="19">
         <f>SUM(January:December!B42)</f>
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C42" s="19">
         <f>SUM(January:December!C42)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D42" s="19">
         <f>SUM(January:December!D42)</f>
@@ -7656,11 +7656,11 @@
       </c>
       <c r="I42" s="19">
         <f>SUM(January:December!I42)</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J42" s="20">
         <f>SUM(January:December!J42)</f>
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -7669,11 +7669,11 @@
       </c>
       <c r="B43" s="22">
         <f>SUM(January:December!B43)</f>
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C43" s="22">
         <f>SUM(January:December!C43)</f>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D43" s="22">
         <f>SUM(January:December!D43)</f>
@@ -7697,11 +7697,11 @@
       </c>
       <c r="I43" s="22">
         <f>SUM(January:December!I43)</f>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J43" s="23">
         <f>SUM(January:December!J43)</f>
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -7710,15 +7710,15 @@
       </c>
       <c r="B44" s="7">
         <f>SUM(January:December!B44)</f>
-        <v>652</v>
+        <v>772</v>
       </c>
       <c r="C44" s="7">
         <f>SUM(January:December!C44)</f>
-        <v>327</v>
+        <v>373</v>
       </c>
       <c r="D44" s="7">
         <f>SUM(January:December!D44)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E44" s="7">
         <f>SUM(January:December!E44)</f>
@@ -7726,11 +7726,11 @@
       </c>
       <c r="F44" s="7">
         <f>SUM(January:December!F44)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G44" s="7">
         <f>SUM(January:December!G44)</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H44" s="7">
         <f>SUM(January:December!H44)</f>
@@ -7738,11 +7738,11 @@
       </c>
       <c r="I44" s="7">
         <f>SUM(January:December!I44)</f>
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="J44" s="8">
         <f>SUM(January:December!J44)</f>
-        <v>358</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -7751,27 +7751,27 @@
       </c>
       <c r="B45" s="10">
         <f>SUM(January:December!B45)</f>
-        <v>6338</v>
+        <v>7448</v>
       </c>
       <c r="C45" s="10">
         <f>SUM(January:December!C45)</f>
-        <v>2862</v>
+        <v>3343</v>
       </c>
       <c r="D45" s="10">
         <f>SUM(January:December!D45)</f>
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="E45" s="10">
         <f>SUM(January:December!E45)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F45" s="10">
         <f>SUM(January:December!F45)</f>
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="G45" s="10">
         <f>SUM(January:December!G45)</f>
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="H45" s="10">
         <f>SUM(January:December!H45)</f>
@@ -7779,11 +7779,11 @@
       </c>
       <c r="I45" s="10">
         <f>SUM(January:December!I45)</f>
-        <v>1926</v>
+        <v>2234</v>
       </c>
       <c r="J45" s="11">
         <f>SUM(January:December!J45)</f>
-        <v>4412</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,27 +7792,27 @@
       </c>
       <c r="B46" s="7">
         <f>SUM(January:December!B46)</f>
-        <v>9556</v>
+        <v>11058</v>
       </c>
       <c r="C46" s="7">
         <f>SUM(January:December!C46)</f>
-        <v>4667</v>
+        <v>5364</v>
       </c>
       <c r="D46" s="7">
         <f>SUM(January:December!D46)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" s="7">
         <f>SUM(January:December!E46)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F46" s="7">
         <f>SUM(January:December!F46)</f>
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="G46" s="7">
         <f>SUM(January:December!G46)</f>
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="H46" s="7">
         <f>SUM(January:December!H46)</f>
@@ -7820,11 +7820,11 @@
       </c>
       <c r="I46" s="7">
         <f>SUM(January:December!I46)</f>
-        <v>1326</v>
+        <v>1522</v>
       </c>
       <c r="J46" s="8">
         <f>SUM(January:December!J46)</f>
-        <v>8230</v>
+        <v>9536</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -7833,15 +7833,15 @@
       </c>
       <c r="B47" s="10">
         <f>SUM(January:December!B47)</f>
-        <v>3020</v>
+        <v>3532</v>
       </c>
       <c r="C47" s="10">
         <f>SUM(January:December!C47)</f>
-        <v>1307</v>
+        <v>1496</v>
       </c>
       <c r="D47" s="10">
         <f>SUM(January:December!D47)</f>
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E47" s="10">
         <f>SUM(January:December!E47)</f>
@@ -7849,23 +7849,23 @@
       </c>
       <c r="F47" s="10">
         <f>SUM(January:December!F47)</f>
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="G47" s="10">
         <f>SUM(January:December!G47)</f>
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="H47" s="10">
         <f>SUM(January:December!H47)</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I47" s="10">
         <f>SUM(January:December!I47)</f>
-        <v>660</v>
+        <v>736</v>
       </c>
       <c r="J47" s="11">
         <f>SUM(January:December!J47)</f>
-        <v>2360</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7874,27 +7874,27 @@
       </c>
       <c r="B48" s="7">
         <f>SUM(January:December!B48)</f>
-        <v>4446</v>
+        <v>5238</v>
       </c>
       <c r="C48" s="7">
         <f>SUM(January:December!C48)</f>
-        <v>1794</v>
+        <v>2138</v>
       </c>
       <c r="D48" s="7">
         <f>SUM(January:December!D48)</f>
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="E48" s="7">
         <f>SUM(January:December!E48)</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(January:December!F48)</f>
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G48" s="7">
         <f>SUM(January:December!G48)</f>
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(January:December!H48)</f>
@@ -7902,11 +7902,11 @@
       </c>
       <c r="I48" s="7">
         <f>SUM(January:December!I48)</f>
-        <v>840</v>
+        <v>1100</v>
       </c>
       <c r="J48" s="8">
         <f>SUM(January:December!J48)</f>
-        <v>3606</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -7915,39 +7915,39 @@
       </c>
       <c r="B49" s="10">
         <f>SUM(January:December!B49)</f>
-        <v>12636</v>
+        <v>14424</v>
       </c>
       <c r="C49" s="10">
         <f>SUM(January:December!C49)</f>
-        <v>5417</v>
+        <v>6165</v>
       </c>
       <c r="D49" s="10">
         <f>SUM(January:December!D49)</f>
-        <v>541</v>
+        <v>651</v>
       </c>
       <c r="E49" s="10">
         <f>SUM(January:December!E49)</f>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F49" s="10">
         <f>SUM(January:December!F49)</f>
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="G49" s="10">
         <f>SUM(January:December!G49)</f>
-        <v>869</v>
+        <v>1012</v>
       </c>
       <c r="H49" s="10">
         <f>SUM(January:December!H49)</f>
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I49" s="10">
         <f>SUM(January:December!I49)</f>
-        <v>2558</v>
+        <v>2910</v>
       </c>
       <c r="J49" s="11">
         <f>SUM(January:December!J49)</f>
-        <v>10078</v>
+        <v>11514</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -7956,39 +7956,39 @@
       </c>
       <c r="B50" s="7">
         <f>SUM(January:December!B50)</f>
-        <v>1471</v>
+        <v>1624</v>
       </c>
       <c r="C50" s="7">
         <f>SUM(January:December!C50)</f>
-        <v>637</v>
+        <v>723</v>
       </c>
       <c r="D50" s="7">
         <f>SUM(January:December!D50)</f>
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E50" s="7">
         <f>SUM(January:December!E50)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F50" s="7">
         <f>SUM(January:December!F50)</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G50" s="7">
         <f>SUM(January:December!G50)</f>
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H50" s="7">
         <f>SUM(January:December!H50)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="7">
         <f>SUM(January:December!I50)</f>
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="J50" s="8">
         <f>SUM(January:December!J50)</f>
-        <v>975</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7997,27 +7997,27 @@
       </c>
       <c r="B51" s="10">
         <f>SUM(January:December!B51)</f>
-        <v>5186</v>
+        <v>5826</v>
       </c>
       <c r="C51" s="10">
         <f>SUM(January:December!C51)</f>
-        <v>2245</v>
+        <v>2539</v>
       </c>
       <c r="D51" s="10">
         <f>SUM(January:December!D51)</f>
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="E51" s="10">
         <f>SUM(January:December!E51)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F51" s="10">
         <f>SUM(January:December!F51)</f>
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G51" s="10">
         <f>SUM(January:December!G51)</f>
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="H51" s="10">
         <f>SUM(January:December!H51)</f>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="I51" s="10">
         <f>SUM(January:December!I51)</f>
-        <v>856</v>
+        <v>1004</v>
       </c>
       <c r="J51" s="11">
         <f>SUM(January:December!J51)</f>
-        <v>4330</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="B52" s="7">
         <f>SUM(January:December!B52)</f>
-        <v>852</v>
+        <v>974</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(January:December!C52)</f>
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="D52" s="7">
         <f>SUM(January:December!D52)</f>
@@ -8054,11 +8054,11 @@
       </c>
       <c r="F52" s="7">
         <f>SUM(January:December!F52)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G52" s="7">
         <f>SUM(January:December!G52)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H52" s="7">
         <f>SUM(January:December!H52)</f>
@@ -8066,11 +8066,11 @@
       </c>
       <c r="I52" s="7">
         <f>SUM(January:December!I52)</f>
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="J52" s="8">
         <f>SUM(January:December!J52)</f>
-        <v>596</v>
+        <v>686</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -8079,11 +8079,11 @@
       </c>
       <c r="B53" s="10">
         <f>SUM(January:December!B53)</f>
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="C53" s="10">
         <f>SUM(January:December!C53)</f>
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="D53" s="10">
         <f>SUM(January:December!D53)</f>
@@ -8107,11 +8107,11 @@
       </c>
       <c r="I53" s="10">
         <f>SUM(January:December!I53)</f>
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="J53" s="11">
         <f>SUM(January:December!J53)</f>
-        <v>165</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -8120,39 +8120,39 @@
       </c>
       <c r="B54" s="7">
         <f>SUM(January:December!B54)</f>
-        <v>4914</v>
+        <v>5584</v>
       </c>
       <c r="C54" s="7">
         <f>SUM(January:December!C54)</f>
-        <v>2357</v>
+        <v>2718</v>
       </c>
       <c r="D54" s="7">
         <f>SUM(January:December!D54)</f>
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E54" s="7">
         <f>SUM(January:December!E54)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="7">
         <f>SUM(January:December!F54)</f>
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="G54" s="7">
         <f>SUM(January:December!G54)</f>
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="H54" s="7">
         <f>SUM(January:December!H54)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
         <f>SUM(January:December!I54)</f>
-        <v>1542</v>
+        <v>1714</v>
       </c>
       <c r="J54" s="8">
         <f>SUM(January:December!J54)</f>
-        <v>3372</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -8161,27 +8161,27 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>4271</v>
+        <v>4849</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>2025</v>
+        <v>2294</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>2029</v>
+        <v>2307</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>2242</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -8202,15 +8202,15 @@
       </c>
       <c r="B56" s="28">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>1134</v>
+        <v>1254</v>
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" si="1"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="G56" s="28">
         <f t="shared" si="1"/>
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="1"/>
@@ -8230,11 +8230,11 @@
       </c>
       <c r="I56" s="28">
         <f t="shared" si="1"/>
-        <v>562</v>
+        <v>614</v>
       </c>
       <c r="J56" s="29">
         <f t="shared" si="1"/>
-        <v>572</v>
+        <v>640</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -8243,39 +8243,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>247202</v>
+        <v>286605</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>105826</v>
+        <v>121924</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>12564</v>
+        <v>14307</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>939</v>
+        <v>1146</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>6641</v>
+        <v>7522</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>20144</v>
+        <v>22975</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>946</v>
+        <v>1062</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>58829</v>
+        <v>67233</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>188373</v>
+        <v>219372</v>
       </c>
     </row>
   </sheetData>
@@ -19532,743 +19532,1697 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="4">
+        <v>3080</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1353</v>
+      </c>
+      <c r="D2" s="4">
+        <v>108</v>
+      </c>
+      <c r="E2" s="4">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4">
+        <v>38</v>
+      </c>
+      <c r="G2" s="4">
+        <v>159</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>472</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2608</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
+      <c r="B3" s="7">
+        <v>1220</v>
+      </c>
+      <c r="C3" s="7">
+        <v>520</v>
+      </c>
+      <c r="D3" s="7">
+        <v>33</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>28</v>
+      </c>
+      <c r="G3" s="7">
+        <v>61</v>
+      </c>
+      <c r="H3" s="7">
+        <v>4</v>
+      </c>
+      <c r="I3" s="7">
+        <v>204</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1016</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="B4" s="10">
+        <v>3186</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1252</v>
+      </c>
+      <c r="D4" s="10">
+        <v>116</v>
+      </c>
+      <c r="E4" s="10">
+        <v>25</v>
+      </c>
+      <c r="F4" s="10">
+        <v>76</v>
+      </c>
+      <c r="G4" s="10">
+        <v>217</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>492</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2694</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
+      <c r="B5" s="7">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>6</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>22</v>
+      </c>
+      <c r="J5" s="8">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="B6" s="10">
+        <v>3082</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1094</v>
+      </c>
+      <c r="D6" s="10">
+        <v>225</v>
+      </c>
+      <c r="E6" s="10">
+        <v>9</v>
+      </c>
+      <c r="F6" s="10">
+        <v>73</v>
+      </c>
+      <c r="G6" s="10">
+        <v>307</v>
+      </c>
+      <c r="H6" s="10">
+        <v>17</v>
+      </c>
+      <c r="I6" s="10">
+        <v>844</v>
+      </c>
+      <c r="J6" s="11">
+        <v>2238</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
+      <c r="B7" s="7">
+        <v>462</v>
+      </c>
+      <c r="C7" s="7">
+        <v>189</v>
+      </c>
+      <c r="D7" s="7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20</v>
+      </c>
+      <c r="G7" s="7">
+        <v>25</v>
+      </c>
+      <c r="H7" s="7">
+        <v>16</v>
+      </c>
+      <c r="I7" s="7">
+        <v>174</v>
+      </c>
+      <c r="J7" s="8">
+        <v>288</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
+      <c r="B8" s="10">
+        <v>202</v>
+      </c>
+      <c r="C8" s="10">
+        <v>108</v>
+      </c>
+      <c r="D8" s="10">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
+        <v>9</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>54</v>
+      </c>
+      <c r="J8" s="11">
+        <v>148</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
+      <c r="B9" s="7">
+        <v>154</v>
+      </c>
+      <c r="C9" s="7">
+        <v>73</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>20</v>
+      </c>
+      <c r="J9" s="8">
+        <v>134</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
+      <c r="B12" s="13">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>4</v>
+      </c>
+      <c r="J12" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="17"/>
+      <c r="B13" s="16">
+        <v>112</v>
+      </c>
+      <c r="C13" s="16">
+        <v>42</v>
+      </c>
+      <c r="D13" s="16">
+        <v>2</v>
+      </c>
+      <c r="E13" s="16">
+        <v>1</v>
+      </c>
+      <c r="F13" s="16">
+        <v>3</v>
+      </c>
+      <c r="G13" s="16">
+        <v>6</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <v>56</v>
+      </c>
+      <c r="J13" s="17">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13">
+        <v>292</v>
+      </c>
+      <c r="C14" s="13">
+        <v>149</v>
+      </c>
+      <c r="D14" s="13">
+        <v>10</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <v>8</v>
+      </c>
+      <c r="G14" s="13">
+        <v>18</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>162</v>
+      </c>
+      <c r="J14" s="14">
+        <v>130</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="16">
+        <v>168</v>
+      </c>
+      <c r="C15" s="16">
+        <v>77</v>
+      </c>
+      <c r="D15" s="16">
+        <v>4</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>11</v>
+      </c>
+      <c r="G15" s="16">
+        <v>15</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
+        <v>56</v>
+      </c>
+      <c r="J15" s="17">
+        <v>112</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="B16" s="10">
+        <v>188</v>
+      </c>
+      <c r="C16" s="10">
+        <v>63</v>
+      </c>
+      <c r="D16" s="10">
+        <v>2</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>3</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>66</v>
+      </c>
+      <c r="J16" s="11">
+        <v>122</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
+      <c r="B17" s="7">
+        <v>1336</v>
+      </c>
+      <c r="C17" s="7">
+        <v>632</v>
+      </c>
+      <c r="D17" s="7">
+        <v>67</v>
+      </c>
+      <c r="E17" s="7">
+        <v>6</v>
+      </c>
+      <c r="F17" s="7">
+        <v>32</v>
+      </c>
+      <c r="G17" s="7">
+        <v>105</v>
+      </c>
+      <c r="H17" s="7">
+        <v>1</v>
+      </c>
+      <c r="I17" s="7">
+        <v>354</v>
+      </c>
+      <c r="J17" s="8">
+        <v>982</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
+      <c r="B18" s="10">
+        <v>82</v>
+      </c>
+      <c r="C18" s="10">
+        <v>42</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <v>32</v>
+      </c>
+      <c r="J18" s="11">
+        <v>50</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="B19" s="7">
+        <v>918</v>
+      </c>
+      <c r="C19" s="7">
+        <v>332</v>
+      </c>
+      <c r="D19" s="7">
+        <v>47</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>8</v>
+      </c>
+      <c r="G19" s="7">
+        <v>56</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <v>242</v>
+      </c>
+      <c r="J19" s="8">
+        <v>676</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11"/>
+      <c r="B20" s="10">
+        <v>10</v>
+      </c>
+      <c r="C20" s="10">
+        <v>6</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>2</v>
+      </c>
+      <c r="G20" s="10">
+        <v>2</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
+        <v>2</v>
+      </c>
+      <c r="J20" s="11">
+        <v>8</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
+      <c r="B21" s="7">
+        <v>589</v>
+      </c>
+      <c r="C21" s="7">
+        <v>463</v>
+      </c>
+      <c r="D21" s="7">
+        <v>6</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7">
+        <v>29</v>
+      </c>
+      <c r="G21" s="7">
+        <v>36</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1</v>
+      </c>
+      <c r="I21" s="7">
+        <v>150</v>
+      </c>
+      <c r="J21" s="8">
+        <v>439</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
+      <c r="B22" s="10">
+        <v>122</v>
+      </c>
+      <c r="C22" s="10">
+        <v>58</v>
+      </c>
+      <c r="D22" s="10">
+        <v>2</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10">
+        <v>6</v>
+      </c>
+      <c r="G22" s="10">
+        <v>8</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>40</v>
+      </c>
+      <c r="J22" s="11">
+        <v>82</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="8"/>
+      <c r="B23" s="7">
+        <v>1676</v>
+      </c>
+      <c r="C23" s="7">
+        <v>567</v>
+      </c>
+      <c r="D23" s="7">
+        <v>173</v>
+      </c>
+      <c r="E23" s="7">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7">
+        <v>43</v>
+      </c>
+      <c r="G23" s="7">
+        <v>229</v>
+      </c>
+      <c r="H23" s="7">
+        <v>2</v>
+      </c>
+      <c r="I23" s="7">
+        <v>306</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1370</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="11"/>
+      <c r="B24" s="10">
+        <v>4890</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1777</v>
+      </c>
+      <c r="D24" s="10">
+        <v>243</v>
+      </c>
+      <c r="E24" s="10">
+        <v>86</v>
+      </c>
+      <c r="F24" s="10">
+        <v>94</v>
+      </c>
+      <c r="G24" s="10">
+        <v>423</v>
+      </c>
+      <c r="H24" s="10">
+        <v>3</v>
+      </c>
+      <c r="I24" s="10">
+        <v>520</v>
+      </c>
+      <c r="J24" s="11">
+        <v>4370</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
+      <c r="B25" s="7">
+        <v>296</v>
+      </c>
+      <c r="C25" s="7">
+        <v>139</v>
+      </c>
+      <c r="D25" s="7">
+        <v>16</v>
+      </c>
+      <c r="E25" s="7">
+        <v>7</v>
+      </c>
+      <c r="F25" s="7">
+        <v>4</v>
+      </c>
+      <c r="G25" s="7">
+        <v>27</v>
+      </c>
+      <c r="H25" s="7">
+        <v>1</v>
+      </c>
+      <c r="I25" s="7">
+        <v>70</v>
+      </c>
+      <c r="J25" s="8">
+        <v>226</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="11"/>
+      <c r="B26" s="10">
+        <v>0</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
+      <c r="B27" s="7">
+        <v>260</v>
+      </c>
+      <c r="C27" s="7">
+        <v>142</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7">
+        <v>14</v>
+      </c>
+      <c r="G27" s="7">
+        <v>16</v>
+      </c>
+      <c r="H27" s="7">
+        <v>2</v>
+      </c>
+      <c r="I27" s="7">
+        <v>124</v>
+      </c>
+      <c r="J27" s="8">
+        <v>136</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11"/>
+      <c r="B28" s="10">
+        <v>370</v>
+      </c>
+      <c r="C28" s="10">
+        <v>137</v>
+      </c>
+      <c r="D28" s="10">
+        <v>28</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10">
+        <v>6</v>
+      </c>
+      <c r="G28" s="10">
+        <v>35</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>106</v>
+      </c>
+      <c r="J28" s="11">
+        <v>264</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
+      <c r="B29" s="7">
+        <v>1156</v>
+      </c>
+      <c r="C29" s="7">
+        <v>521</v>
+      </c>
+      <c r="D29" s="7">
+        <v>12</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7">
+        <v>22</v>
+      </c>
+      <c r="G29" s="7">
+        <v>34</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7">
+        <v>182</v>
+      </c>
+      <c r="J29" s="8">
+        <v>974</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="11"/>
+      <c r="B30" s="10">
+        <v>46</v>
+      </c>
+      <c r="C30" s="10">
+        <v>17</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10">
+        <v>2</v>
+      </c>
+      <c r="G30" s="10">
+        <v>2</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
+        <v>16</v>
+      </c>
+      <c r="J30" s="11">
+        <v>30</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="8"/>
+      <c r="B31" s="7">
+        <v>44</v>
+      </c>
+      <c r="C31" s="7">
+        <v>13</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="7">
+        <v>2</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1</v>
+      </c>
+      <c r="I31" s="7">
+        <v>16</v>
+      </c>
+      <c r="J31" s="8">
+        <v>28</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="11"/>
+      <c r="B32" s="10">
+        <v>1348</v>
+      </c>
+      <c r="C32" s="10">
+        <v>452</v>
+      </c>
+      <c r="D32" s="10">
+        <v>79</v>
+      </c>
+      <c r="E32" s="10">
+        <v>2</v>
+      </c>
+      <c r="F32" s="10">
+        <v>58</v>
+      </c>
+      <c r="G32" s="10">
+        <v>139</v>
+      </c>
+      <c r="H32" s="10">
+        <v>6</v>
+      </c>
+      <c r="I32" s="10">
+        <v>434</v>
+      </c>
+      <c r="J32" s="11">
+        <v>914</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
+      <c r="B33" s="7">
+        <v>1184</v>
+      </c>
+      <c r="C33" s="7">
+        <v>390</v>
+      </c>
+      <c r="D33" s="7">
+        <v>16</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>50</v>
+      </c>
+      <c r="G33" s="7">
+        <v>66</v>
+      </c>
+      <c r="H33" s="7">
+        <v>17</v>
+      </c>
+      <c r="I33" s="7">
+        <v>498</v>
+      </c>
+      <c r="J33" s="8">
+        <v>686</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="11"/>
+      <c r="B34" s="10">
+        <v>246</v>
+      </c>
+      <c r="C34" s="10">
+        <v>134</v>
+      </c>
+      <c r="D34" s="10">
+        <v>8</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10">
+        <v>5</v>
+      </c>
+      <c r="G34" s="10">
+        <v>14</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>62</v>
+      </c>
+      <c r="J34" s="11">
+        <v>184</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
+      <c r="B35" s="7">
+        <v>3138</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1264</v>
+      </c>
+      <c r="D35" s="7">
+        <v>170</v>
+      </c>
+      <c r="E35" s="7">
+        <v>16</v>
+      </c>
+      <c r="F35" s="7">
+        <v>67</v>
+      </c>
+      <c r="G35" s="7">
+        <v>253</v>
+      </c>
+      <c r="H35" s="7">
+        <v>14</v>
+      </c>
+      <c r="I35" s="7">
+        <v>516</v>
+      </c>
+      <c r="J35" s="8">
+        <v>2622</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="11"/>
+      <c r="B36" s="10">
+        <v>388</v>
+      </c>
+      <c r="C36" s="10">
+        <v>161</v>
+      </c>
+      <c r="D36" s="10">
+        <v>10</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0</v>
+      </c>
+      <c r="F36" s="10">
+        <v>4</v>
+      </c>
+      <c r="G36" s="10">
+        <v>14</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>90</v>
+      </c>
+      <c r="J36" s="11">
+        <v>298</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
+      <c r="B37" s="7">
+        <v>1258</v>
+      </c>
+      <c r="C37" s="7">
+        <v>474</v>
+      </c>
+      <c r="D37" s="7">
+        <v>102</v>
+      </c>
+      <c r="E37" s="7">
+        <v>4</v>
+      </c>
+      <c r="F37" s="7">
+        <v>20</v>
+      </c>
+      <c r="G37" s="7">
+        <v>126</v>
+      </c>
+      <c r="H37" s="7">
+        <v>2</v>
+      </c>
+      <c r="I37" s="7">
+        <v>234</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1024</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
+      <c r="B38" s="10">
+        <v>41</v>
+      </c>
+      <c r="C38" s="10">
+        <v>34</v>
+      </c>
+      <c r="D38" s="10">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0</v>
+      </c>
+      <c r="F38" s="10">
+        <v>2</v>
+      </c>
+      <c r="G38" s="10">
+        <v>2</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>4</v>
+      </c>
+      <c r="J38" s="11">
+        <v>37</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="8"/>
+      <c r="B39" s="7">
+        <v>206</v>
+      </c>
+      <c r="C39" s="7">
+        <v>53</v>
+      </c>
+      <c r="D39" s="7">
+        <v>19</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7">
+        <v>19</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>76</v>
+      </c>
+      <c r="J39" s="8">
+        <v>130</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="20"/>
+      <c r="B40" s="19">
+        <v>14</v>
+      </c>
+      <c r="C40" s="19">
+        <v>4</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>0</v>
+      </c>
+      <c r="I40" s="19">
+        <v>6</v>
+      </c>
+      <c r="J40" s="20">
+        <v>8</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="23"/>
+      <c r="B41" s="22">
+        <v>50</v>
+      </c>
+      <c r="C41" s="22">
+        <v>3</v>
+      </c>
+      <c r="D41" s="22">
+        <v>1</v>
+      </c>
+      <c r="E41" s="22">
+        <v>0</v>
+      </c>
+      <c r="F41" s="22">
+        <v>0</v>
+      </c>
+      <c r="G41" s="22">
+        <v>1</v>
+      </c>
+      <c r="H41" s="22">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22">
+        <v>20</v>
+      </c>
+      <c r="J41" s="23">
+        <v>30</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20"/>
+      <c r="B42" s="19">
+        <v>34</v>
+      </c>
+      <c r="C42" s="19">
+        <v>10</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19">
+        <v>16</v>
+      </c>
+      <c r="J42" s="20">
+        <v>18</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="23"/>
+      <c r="B43" s="22">
+        <v>22</v>
+      </c>
+      <c r="C43" s="22">
+        <v>5</v>
+      </c>
+      <c r="D43" s="22">
+        <v>0</v>
+      </c>
+      <c r="E43" s="22">
+        <v>0</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22">
+        <v>0</v>
+      </c>
+      <c r="H43" s="22">
+        <v>0</v>
+      </c>
+      <c r="I43" s="22">
+        <v>10</v>
+      </c>
+      <c r="J43" s="23">
+        <v>12</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="8"/>
+      <c r="B44" s="7">
+        <v>120</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46</v>
+      </c>
+      <c r="D44" s="7">
+        <v>4</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
+        <v>6</v>
+      </c>
+      <c r="H44" s="7">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <v>42</v>
+      </c>
+      <c r="J44" s="8">
+        <v>78</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="11"/>
+      <c r="B45" s="10">
+        <v>1110</v>
+      </c>
+      <c r="C45" s="10">
+        <v>481</v>
+      </c>
+      <c r="D45" s="10">
+        <v>24</v>
+      </c>
+      <c r="E45" s="10">
+        <v>3</v>
+      </c>
+      <c r="F45" s="10">
+        <v>14</v>
+      </c>
+      <c r="G45" s="10">
+        <v>41</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10">
+        <v>308</v>
+      </c>
+      <c r="J45" s="11">
+        <v>802</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
+      <c r="B46" s="7">
+        <v>1502</v>
+      </c>
+      <c r="C46" s="7">
+        <v>697</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>3</v>
+      </c>
+      <c r="F46" s="7">
+        <v>27</v>
+      </c>
+      <c r="G46" s="7">
+        <v>31</v>
+      </c>
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>196</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1306</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="11"/>
+      <c r="B47" s="10">
+        <v>512</v>
+      </c>
+      <c r="C47" s="10">
+        <v>189</v>
+      </c>
+      <c r="D47" s="10">
+        <v>6</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0</v>
+      </c>
+      <c r="F47" s="10">
+        <v>38</v>
+      </c>
+      <c r="G47" s="10">
+        <v>44</v>
+      </c>
+      <c r="H47" s="10">
+        <v>11</v>
+      </c>
+      <c r="I47" s="10">
+        <v>76</v>
+      </c>
+      <c r="J47" s="11">
+        <v>436</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="8"/>
+      <c r="B48" s="7">
+        <v>792</v>
+      </c>
+      <c r="C48" s="7">
+        <v>344</v>
+      </c>
+      <c r="D48" s="7">
+        <v>35</v>
+      </c>
+      <c r="E48" s="7">
+        <v>3</v>
+      </c>
+      <c r="F48" s="7">
+        <v>9</v>
+      </c>
+      <c r="G48" s="7">
+        <v>47</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>260</v>
+      </c>
+      <c r="J48" s="8">
+        <v>532</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="11"/>
+      <c r="B49" s="10">
+        <v>1788</v>
+      </c>
+      <c r="C49" s="10">
+        <v>748</v>
+      </c>
+      <c r="D49" s="10">
+        <v>110</v>
+      </c>
+      <c r="E49" s="10">
+        <v>4</v>
+      </c>
+      <c r="F49" s="10">
+        <v>29</v>
+      </c>
+      <c r="G49" s="10">
+        <v>143</v>
+      </c>
+      <c r="H49" s="10">
+        <v>11</v>
+      </c>
+      <c r="I49" s="10">
+        <v>352</v>
+      </c>
+      <c r="J49" s="11">
+        <v>1436</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="8"/>
+      <c r="B50" s="7">
+        <v>153</v>
+      </c>
+      <c r="C50" s="7">
+        <v>86</v>
+      </c>
+      <c r="D50" s="7">
+        <v>10</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2</v>
+      </c>
+      <c r="F50" s="7">
+        <v>4</v>
+      </c>
+      <c r="G50" s="7">
+        <v>16</v>
+      </c>
+      <c r="H50" s="7">
+        <v>1</v>
+      </c>
+      <c r="I50" s="7">
+        <v>20</v>
+      </c>
+      <c r="J50" s="8">
+        <v>133</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
+      <c r="B51" s="10">
+        <v>640</v>
+      </c>
+      <c r="C51" s="10">
+        <v>294</v>
+      </c>
+      <c r="D51" s="10">
+        <v>25</v>
+      </c>
+      <c r="E51" s="10">
+        <v>1</v>
+      </c>
+      <c r="F51" s="10">
+        <v>10</v>
+      </c>
+      <c r="G51" s="10">
+        <v>36</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0</v>
+      </c>
+      <c r="I51" s="10">
+        <v>148</v>
+      </c>
+      <c r="J51" s="11">
+        <v>492</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="8"/>
+      <c r="B52" s="7">
+        <v>122</v>
+      </c>
+      <c r="C52" s="7">
+        <v>55</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1</v>
+      </c>
+      <c r="H52" s="7">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7">
+        <v>32</v>
+      </c>
+      <c r="J52" s="8">
+        <v>90</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="11"/>
+      <c r="B53" s="10">
+        <v>88</v>
+      </c>
+      <c r="C53" s="10">
+        <v>33</v>
+      </c>
+      <c r="D53" s="10">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10">
+        <v>0</v>
+      </c>
+      <c r="G53" s="10">
+        <v>0</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10">
+        <v>46</v>
+      </c>
+      <c r="J53" s="11">
+        <v>42</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="8"/>
+      <c r="B54" s="7">
+        <v>670</v>
+      </c>
+      <c r="C54" s="7">
+        <v>361</v>
+      </c>
+      <c r="D54" s="7">
+        <v>11</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2</v>
+      </c>
+      <c r="F54" s="7">
+        <v>14</v>
+      </c>
+      <c r="G54" s="7">
+        <v>27</v>
+      </c>
+      <c r="H54" s="7">
+        <v>2</v>
+      </c>
+      <c r="I54" s="7">
+        <v>172</v>
+      </c>
+      <c r="J54" s="8">
+        <v>498</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
@@ -20276,27 +21230,27 @@
       </c>
       <c r="B55" s="31">
         <f>SUM(B12,B13,B14,B15)</f>
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="C55" s="31">
         <f t="shared" ref="C55:J55" si="0">SUM(C12,C13,C14,C15)</f>
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H55" s="31">
         <f t="shared" si="0"/>
@@ -20304,11 +21258,11 @@
       </c>
       <c r="I55" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -20317,15 +21271,15 @@
       </c>
       <c r="B56" s="28">
         <f>SUM(B40,B41,B42,B43)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C56" s="28">
         <f t="shared" ref="C56:J56" si="1">SUM(C40,C41,C42,C43)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" si="1"/>
@@ -20337,7 +21291,7 @@
       </c>
       <c r="G56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="1"/>
@@ -20345,11 +21299,11 @@
       </c>
       <c r="I56" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J56" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -20358,39 +21312,39 @@
       </c>
       <c r="B57" s="25">
         <f>SUM(B2:B54)</f>
-        <v>0</v>
+        <v>39403</v>
       </c>
       <c r="C57" s="25">
         <f t="shared" ref="C57:J57" si="2">SUM(C2:C54)</f>
-        <v>0</v>
+        <v>16098</v>
       </c>
       <c r="D57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="E57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="F57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>881</v>
       </c>
       <c r="G57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2831</v>
       </c>
       <c r="H57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I57" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8404</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30999</v>
       </c>
     </row>
   </sheetData>
